--- a/Scopus.xlsx
+++ b/Scopus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\SysLitRev-V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0189122-DE28-4688-B7CD-58E834B19BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E81C0C-8A15-414D-9FB9-CDD77ED51492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="2755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4461" uniqueCount="2762">
   <si>
     <t>Authors</t>
   </si>
@@ -8290,6 +8290,27 @@
   </si>
   <si>
     <t>7201968604;</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Proc</t>
+  </si>
+  <si>
+    <t>Same Book</t>
+  </si>
+  <si>
+    <t>Similar</t>
+  </si>
+  <si>
+    <t>Paywall</t>
+  </si>
+  <si>
+    <t>Not English</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
@@ -8613,9 +8634,10 @@
   <cols>
     <col min="1" max="1" width="2.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="5.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" customWidth="1"/>
     <col min="5" max="5" width="93.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="41" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8961,6 +8983,9 @@
       <c r="B8" t="s">
         <v>1924</v>
       </c>
+      <c r="C8" t="s">
+        <v>2755</v>
+      </c>
       <c r="D8">
         <v>7</v>
       </c>
@@ -11000,6 +11025,9 @@
       <c r="B48" t="s">
         <v>2010</v>
       </c>
+      <c r="C48" t="s">
+        <v>2755</v>
+      </c>
       <c r="D48">
         <v>47</v>
       </c>
@@ -11553,6 +11581,9 @@
       <c r="B59" t="s">
         <v>2036</v>
       </c>
+      <c r="C59" t="s">
+        <v>2756</v>
+      </c>
       <c r="D59">
         <v>58</v>
       </c>
@@ -14354,6 +14385,9 @@
       <c r="B114" t="s">
         <v>2148</v>
       </c>
+      <c r="C114" t="s">
+        <v>2755</v>
+      </c>
       <c r="D114">
         <v>113</v>
       </c>
@@ -14931,6 +14965,9 @@
       <c r="B125" t="s">
         <v>2170</v>
       </c>
+      <c r="C125" t="s">
+        <v>2757</v>
+      </c>
       <c r="D125">
         <v>124</v>
       </c>
@@ -14978,6 +15015,9 @@
       <c r="B126" t="s">
         <v>2170</v>
       </c>
+      <c r="C126" t="s">
+        <v>2757</v>
+      </c>
       <c r="D126">
         <v>125</v>
       </c>
@@ -15025,6 +15065,9 @@
       <c r="B127" t="s">
         <v>2170</v>
       </c>
+      <c r="C127" t="s">
+        <v>2757</v>
+      </c>
       <c r="D127">
         <v>126</v>
       </c>
@@ -15072,6 +15115,9 @@
       <c r="B128" t="s">
         <v>2170</v>
       </c>
+      <c r="C128" t="s">
+        <v>2757</v>
+      </c>
       <c r="D128">
         <v>127</v>
       </c>
@@ -15119,6 +15165,9 @@
       <c r="B129" t="s">
         <v>2170</v>
       </c>
+      <c r="C129" t="s">
+        <v>2757</v>
+      </c>
       <c r="D129">
         <v>128</v>
       </c>
@@ -15166,6 +15215,9 @@
       <c r="B130" t="s">
         <v>2170</v>
       </c>
+      <c r="C130" t="s">
+        <v>2757</v>
+      </c>
       <c r="D130">
         <v>129</v>
       </c>
@@ -15213,6 +15265,9 @@
       <c r="B131" t="s">
         <v>2170</v>
       </c>
+      <c r="C131" t="s">
+        <v>2757</v>
+      </c>
       <c r="D131">
         <v>130</v>
       </c>
@@ -15263,6 +15318,9 @@
       <c r="B132" t="s">
         <v>2170</v>
       </c>
+      <c r="C132" t="s">
+        <v>2757</v>
+      </c>
       <c r="D132">
         <v>131</v>
       </c>
@@ -15313,6 +15371,9 @@
       <c r="B133" t="s">
         <v>2170</v>
       </c>
+      <c r="C133" t="s">
+        <v>2757</v>
+      </c>
       <c r="D133">
         <v>132</v>
       </c>
@@ -15713,6 +15774,9 @@
       <c r="B141" t="s">
         <v>2188</v>
       </c>
+      <c r="C141" t="s">
+        <v>2755</v>
+      </c>
       <c r="D141">
         <v>140</v>
       </c>
@@ -16381,6 +16445,9 @@
       <c r="B154" t="s">
         <v>2215</v>
       </c>
+      <c r="C154" t="s">
+        <v>2755</v>
+      </c>
       <c r="D154">
         <v>153</v>
       </c>
@@ -17273,6 +17340,9 @@
       <c r="B171" t="s">
         <v>2247</v>
       </c>
+      <c r="C171" t="s">
+        <v>2756</v>
+      </c>
       <c r="D171">
         <v>170</v>
       </c>
@@ -17314,6 +17384,9 @@
       <c r="B172" t="s">
         <v>2249</v>
       </c>
+      <c r="C172" t="s">
+        <v>2755</v>
+      </c>
       <c r="D172">
         <v>171</v>
       </c>
@@ -18132,6 +18205,9 @@
       <c r="B188" t="s">
         <v>2279</v>
       </c>
+      <c r="C188" t="s">
+        <v>2758</v>
+      </c>
       <c r="D188">
         <v>187</v>
       </c>
@@ -18903,6 +18979,9 @@
       <c r="B203" t="s">
         <v>2307</v>
       </c>
+      <c r="C203" t="s">
+        <v>2755</v>
+      </c>
       <c r="D203">
         <v>202</v>
       </c>
@@ -18950,6 +19029,9 @@
       <c r="B204" t="s">
         <v>2036</v>
       </c>
+      <c r="C204" t="s">
+        <v>2756</v>
+      </c>
       <c r="D204">
         <v>203</v>
       </c>
@@ -19886,6 +19968,9 @@
       <c r="B222" t="s">
         <v>2343</v>
       </c>
+      <c r="C222" t="s">
+        <v>2759</v>
+      </c>
       <c r="D222">
         <v>221</v>
       </c>
@@ -20130,6 +20215,9 @@
       <c r="B227" t="s">
         <v>2289</v>
       </c>
+      <c r="C227" t="s">
+        <v>2759</v>
+      </c>
       <c r="D227">
         <v>226</v>
       </c>
@@ -21331,6 +21419,9 @@
       <c r="B250" t="s">
         <v>2395</v>
       </c>
+      <c r="C250" t="s">
+        <v>2759</v>
+      </c>
       <c r="D250">
         <v>249</v>
       </c>
@@ -22743,6 +22834,9 @@
       <c r="B278" t="s">
         <v>2451</v>
       </c>
+      <c r="C278" t="s">
+        <v>2760</v>
+      </c>
       <c r="D278">
         <v>277</v>
       </c>
@@ -23358,6 +23452,9 @@
       <c r="B290" t="s">
         <v>2476</v>
       </c>
+      <c r="C290" t="s">
+        <v>2759</v>
+      </c>
       <c r="D290">
         <v>289</v>
       </c>
@@ -23826,6 +23923,9 @@
       <c r="B299" t="s">
         <v>2494</v>
       </c>
+      <c r="C299" t="s">
+        <v>2759</v>
+      </c>
       <c r="D299">
         <v>298</v>
       </c>
@@ -25341,6 +25441,9 @@
       </c>
       <c r="B328" t="s">
         <v>2550</v>
+      </c>
+      <c r="C328" t="s">
+        <v>2761</v>
       </c>
       <c r="D328">
         <v>327</v>

--- a/Scopus.xlsx
+++ b/Scopus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\SysLitRev-V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E81C0C-8A15-414D-9FB9-CDD77ED51492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ADB5E4-45F9-408A-975A-1946899AF187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4461" uniqueCount="2762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4473" uniqueCount="2762">
   <si>
     <t>Authors</t>
   </si>
@@ -25442,9 +25442,6 @@
       <c r="B328" t="s">
         <v>2550</v>
       </c>
-      <c r="C328" t="s">
-        <v>2761</v>
-      </c>
       <c r="D328">
         <v>327</v>
       </c>
@@ -25489,6 +25486,9 @@
       <c r="B329" t="s">
         <v>2552</v>
       </c>
+      <c r="C329" t="s">
+        <v>2755</v>
+      </c>
       <c r="D329">
         <v>328</v>
       </c>
@@ -25786,6 +25786,9 @@
       <c r="B335" t="s">
         <v>2564</v>
       </c>
+      <c r="C335" t="s">
+        <v>985</v>
+      </c>
       <c r="D335">
         <v>334</v>
       </c>
@@ -26033,6 +26036,9 @@
       <c r="B340" t="s">
         <v>2572</v>
       </c>
+      <c r="C340" t="s">
+        <v>2761</v>
+      </c>
       <c r="D340">
         <v>339</v>
       </c>
@@ -26751,6 +26757,9 @@
       <c r="B354" t="s">
         <v>2600</v>
       </c>
+      <c r="C354" t="s">
+        <v>2755</v>
+      </c>
       <c r="D354">
         <v>353</v>
       </c>
@@ -27234,6 +27243,9 @@
       <c r="B363" t="s">
         <v>2618</v>
       </c>
+      <c r="C363" t="s">
+        <v>2759</v>
+      </c>
       <c r="D363">
         <v>362</v>
       </c>
@@ -27608,6 +27620,9 @@
       <c r="B370" t="s">
         <v>2632</v>
       </c>
+      <c r="C370" t="s">
+        <v>2755</v>
+      </c>
       <c r="D370">
         <v>369</v>
       </c>
@@ -29230,6 +29245,9 @@
       <c r="B401" t="s">
         <v>2694</v>
       </c>
+      <c r="C401" t="s">
+        <v>2755</v>
+      </c>
       <c r="D401">
         <v>400</v>
       </c>
@@ -29321,6 +29339,9 @@
       <c r="B403" t="s">
         <v>2698</v>
       </c>
+      <c r="C403" t="s">
+        <v>2759</v>
+      </c>
       <c r="D403">
         <v>402</v>
       </c>
@@ -29374,6 +29395,9 @@
       <c r="B404" t="s">
         <v>2700</v>
       </c>
+      <c r="C404" t="s">
+        <v>2755</v>
+      </c>
       <c r="D404">
         <v>403</v>
       </c>
@@ -29901,6 +29925,9 @@
       <c r="B414" t="s">
         <v>2720</v>
       </c>
+      <c r="C414" t="s">
+        <v>2755</v>
+      </c>
       <c r="D414">
         <v>413</v>
       </c>
@@ -30054,6 +30081,9 @@
       <c r="B417" t="s">
         <v>2726</v>
       </c>
+      <c r="C417" t="s">
+        <v>2755</v>
+      </c>
       <c r="D417">
         <v>416</v>
       </c>
@@ -30404,6 +30434,9 @@
       <c r="B424" t="s">
         <v>2740</v>
       </c>
+      <c r="C424" t="s">
+        <v>2755</v>
+      </c>
       <c r="D424">
         <v>423</v>
       </c>
@@ -30651,6 +30684,9 @@
       <c r="B429" t="s">
         <v>2750</v>
       </c>
+      <c r="C429" t="s">
+        <v>2755</v>
+      </c>
       <c r="D429">
         <v>428</v>
       </c>
@@ -30790,5 +30826,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Scopus.xlsx
+++ b/Scopus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\SysLitRev-V2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAU\My Folder\Github\SysLitRev-V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ADB5E4-45F9-408A-975A-1946899AF187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84575A66-5DA9-4CA9-B803-E28C9308FE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8326,12 +8326,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -8346,9 +8352,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9083,7 +9090,7 @@
       <c r="D10">
         <v>9</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F10">
@@ -9283,7 +9290,7 @@
       <c r="D14">
         <v>13</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>470</v>
       </c>
       <c r="F14">
@@ -13741,7 +13748,7 @@
       <c r="D101">
         <v>100</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="2" t="s">
         <v>136</v>
       </c>
       <c r="F101">
@@ -14132,7 +14139,7 @@
       <c r="D109">
         <v>108</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="2" t="s">
         <v>893</v>
       </c>
       <c r="F109">
@@ -15474,7 +15481,7 @@
       <c r="D135">
         <v>134</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="2" t="s">
         <v>534</v>
       </c>
       <c r="F135">
@@ -17187,7 +17194,7 @@
       <c r="D168">
         <v>167</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="2" t="s">
         <v>674</v>
       </c>
       <c r="F168">
@@ -17543,7 +17550,7 @@
       <c r="D175">
         <v>174</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="2" t="s">
         <v>538</v>
       </c>
       <c r="F175">
@@ -27944,7 +27951,7 @@
       <c r="D376">
         <v>375</v>
       </c>
-      <c r="E376" t="s">
+      <c r="E376" s="2" t="s">
         <v>1456</v>
       </c>
       <c r="F376">
@@ -28527,7 +28534,7 @@
       <c r="D387">
         <v>386</v>
       </c>
-      <c r="E387" t="s">
+      <c r="E387" s="2" t="s">
         <v>1519</v>
       </c>
       <c r="F387">
